--- a/artfynd/A 33519-2024 artfynd.xlsx
+++ b/artfynd/A 33519-2024 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>122753476</v>
       </c>
       <c r="B7" t="n">
-        <v>89991</v>
+        <v>89995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 33519-2024 artfynd.xlsx
+++ b/artfynd/A 33519-2024 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>122753476</v>
       </c>
       <c r="B7" t="n">
-        <v>89995</v>
+        <v>89998</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 33519-2024 artfynd.xlsx
+++ b/artfynd/A 33519-2024 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>122753476</v>
       </c>
       <c r="B7" t="n">
-        <v>89998</v>
+        <v>90000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 33519-2024 artfynd.xlsx
+++ b/artfynd/A 33519-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113678855</v>
+        <v>113680143</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616871</v>
+        <v>616961</v>
       </c>
       <c r="R2" t="n">
-        <v>7034172</v>
+        <v>7034272</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,12 +757,12 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680169</v>
+        <v>113680148</v>
       </c>
       <c r="B3" t="n">
-        <v>93204</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616873</v>
+        <v>616938</v>
       </c>
       <c r="R3" t="n">
-        <v>7034184</v>
+        <v>7034269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113678858</v>
+        <v>113680142</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>92406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616871</v>
+        <v>616954</v>
       </c>
       <c r="R4" t="n">
-        <v>7034175</v>
+        <v>7034272</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,12 +969,12 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680170</v>
+        <v>113680144</v>
       </c>
       <c r="B5" t="n">
-        <v>93220</v>
+        <v>92406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616886</v>
+        <v>616957</v>
       </c>
       <c r="R5" t="n">
-        <v>7034100</v>
+        <v>7034264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113678826</v>
+        <v>122753476</v>
       </c>
       <c r="B6" t="n">
-        <v>79332</v>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Ång</t>
+          <t>Renskinns- V, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616849</v>
+        <v>616886</v>
       </c>
       <c r="R6" t="n">
-        <v>7034218</v>
+        <v>7034105</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,11 +1180,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1205,50 +1200,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122753476</v>
+        <v>113680170</v>
       </c>
       <c r="B7" t="n">
-        <v>90000</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Slåttesmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>616886</v>
       </c>
       <c r="R7" t="n">
-        <v>7034105</v>
+        <v>7034100</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,6 +1283,11 @@
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AW7" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1305,7 +1300,648 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113680169</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>616873</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7034184</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113678826</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>616849</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7034218</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113678855</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>616871</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7034172</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113678858</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>616871</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7034175</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113678839</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>616965</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7034263</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113682594</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>616858</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7034324</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 33519-2024 artfynd.xlsx
+++ b/artfynd/A 33519-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680143</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680142</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680144</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122753476</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680170</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680169</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678826</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678855</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678858</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1831,6 +1886,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678839</t>
         </is>
       </c>
     </row>
@@ -1944,8 +2004,27 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113682594</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>